--- a/测试用例_硬盘扫描专项.xlsx
+++ b/测试用例_硬盘扫描专项.xlsx
@@ -4,12 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12375" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="G盘-资源准备" sheetId="1" r:id="rId1"/>
     <sheet name="5情况x4状态" sheetId="2" r:id="rId2"/>
     <sheet name="一轮测试，G盘" sheetId="3" r:id="rId3"/>
+    <sheet name="一轮测试，I盘（移动硬盘）" sheetId="4" r:id="rId4"/>
+    <sheet name="一轮测试，K盘（SD卡）" sheetId="5" r:id="rId5"/>
+    <sheet name="一轮测试，J盘（U盘存储）" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1023" uniqueCount="382">
   <si>
     <t>G: 测试资源准备</t>
   </si>
@@ -746,6 +749,435 @@
   </si>
   <si>
     <t>能检出；10 层路径完整</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I: 移动盘（465gb）功能用例 </t>
+  </si>
+  <si>
+    <t>用途： 范围：仅 i: 移动硬盘（465GB HDD，最稳定）</t>
+  </si>
+  <si>
+    <t>资源准备：见 sheet「盘-资源准备」</t>
+  </si>
+  <si>
+    <t>在 I： 盘中删除文件并在回收站保留；所有文件直接放 I： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 I： 根目录，删除到回收站且不清空回收站，扫描 I：，在结果中搜索目标文件名</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>在 I： 盘中删除文件并在回收站保留；所有文件直接放 I： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 I： 根目录，删除到回收站且不清空回收站，扫描 I：，打开结果详情查看路径</t>
+  </si>
+  <si>
+    <t>展示删除前路径（应为 I：\文件名），路径可读且无乱码</t>
+  </si>
+  <si>
+    <t>在 I： 盘中删除文件并在回收站保留；所有文件直接放 I： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 I： 根目录，删除到回收站且不清空回收站，扫描 I：，在结果中点击预览</t>
+  </si>
+  <si>
+    <t>在 I： 盘中删除文件并在回收站保留；所有文件直接放 I： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 I： 根目录，删除到回收站且不清空回收站，扫描 I：，导出或恢复后本地打开核对内容</t>
+  </si>
+  <si>
+    <t>在 I： 盘中删除文件并清空回收站；所有文件直接放 I： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 I： 根目录，删除到回收站后立即清空回收站，扫描 I：，在结果中搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 I： 盘中删除文件并清空回收站；所有文件直接放 I： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 I： 根目录，删除到回收站后立即清空回收站，扫描 I：，打开结果详情查看路径</t>
+  </si>
+  <si>
+    <t>在 I： 盘中删除文件并清空回收站；所有文件直接放 I： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 I： 根目录，删除到回收站后立即清空回收站，扫描 I：，在结果中点击预览</t>
+  </si>
+  <si>
+    <t>在 I： 盘中删除文件并清空回收站；所有文件直接放 I： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 I： 根目录，删除到回收站后立即清空回收站，扫描 I：，导出或恢复后本地打开核对内容</t>
+  </si>
+  <si>
+    <t>在 I： 盘展示/识别隐藏文件（未删除）；文件直接放 I： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>样本放 I： 根目录并设为 Hidden（不删除），扫描 I：，搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 I： 盘展示/识别隐藏文件（未删除）；文件直接放 I： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 I： 盘展示/识别隐藏文件（未删除）；文件直接放 I： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 I： 盘展示/识别隐藏文件（未删除）；文件直接放 I： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 I： 盘中直接永久删除文件（不进回收站）；所有文件直接放 I： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 将样本文件直接放 I： 根目录；2) 选中文件按 Shift+Delete 并确认“永久删除”；3) 打开回收站确认看不到该文件；4) 扫描 I： 并搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 I： 盘中直接永久删除文件（不进回收站）；所有文件直接放 I： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 I： 盘中直接永久删除文件（不进回收站）；所有文件直接放 I： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 I： 盘中直接永久删除文件（不进回收站）；所有文件直接放 I： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并删除到回收站保留；文件直接放 I： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 样本放 I： 根目录并设为隐藏；2) 删除到回收站且不清空回收站；3) 扫描 I：；4) 搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并删除到回收站保留；文件直接放 I： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并删除到回收站保留；文件直接放 I： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并删除到回收站保留；文件直接放 I： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并删除后清空回收站；文件直接放 I： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 样本放 I： 根目录并设为隐藏；2) 删除到回收站后立即清空回收站；3) 扫描 I：；4) 搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并删除后清空回收站；文件直接放 I： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并删除后清空回收站；文件直接放 I： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并删除后清空回收站；文件直接放 I： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 I： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 样本放 I： 根目录并设为隐藏；2) Shift+Delete 永久删除；3) 回收站确认无该文件；4) 扫描 I： 并搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 I： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 I： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 I： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 I： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>1) 运行 stage_g_folder_samples.ps1 或建 I：\nest_L1\；2) 样本名 G_nest_L01_&lt;yyMMdd_HHmm&gt;.pptx；3) Delete→回收站保留；4) 扫 I： 看路径</t>
+  </si>
+  <si>
+    <t>能检出；路径含 I：\nest_L1\G_nest_L01_…</t>
+  </si>
+  <si>
+    <t>同上，路径 I：\nest_L1\nest_L2\nest_L3\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K盘: SD卡（16gb）功能用例 </t>
+  </si>
+  <si>
+    <t>用途： 范围：仅 : SD卡（16G）</t>
+  </si>
+  <si>
+    <t>在 K： 盘中删除文件并在回收站保留；所有文件直接放 K： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 K： 根目录，删除到回收站且不清空回收站，扫描 K：，在结果中搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 K： 盘中删除文件并在回收站保留；所有文件直接放 K： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 K： 根目录，删除到回收站且不清空回收站，扫描 K：，打开结果详情查看路径</t>
+  </si>
+  <si>
+    <t>展示删除前路径（应为 K：\文件名），路径可读且无乱码</t>
+  </si>
+  <si>
+    <t>在 K： 盘中删除文件并在回收站保留；所有文件直接放 K： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 K： 根目录，删除到回收站且不清空回收站，扫描 K：，在结果中点击预览</t>
+  </si>
+  <si>
+    <t>在 K： 盘中删除文件并在回收站保留；所有文件直接放 K： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 K： 根目录，删除到回收站且不清空回收站，扫描 K：，导出或恢复后本地打开核对内容</t>
+  </si>
+  <si>
+    <t>在 K： 盘中删除文件并清空回收站；所有文件直接放 K： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 K： 根目录，删除到回收站后立即清空回收站，扫描 K：，在结果中搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 K： 盘中删除文件并清空回收站；所有文件直接放 K： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 K： 根目录，删除到回收站后立即清空回收站，扫描 K：，打开结果详情查看路径</t>
+  </si>
+  <si>
+    <t>在 K： 盘中删除文件并清空回收站；所有文件直接放 K： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 K： 根目录，删除到回收站后立即清空回收站，扫描 K：，在结果中点击预览</t>
+  </si>
+  <si>
+    <t>在 K： 盘中删除文件并清空回收站；所有文件直接放 K： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 K： 根目录，删除到回收站后立即清空回收站，扫描 K：，导出或恢复后本地打开核对内容</t>
+  </si>
+  <si>
+    <t>在 K： 盘展示/识别隐藏文件（未删除）；文件直接放 K： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>样本放 K： 根目录并设为 Hidden（不删除），扫描 K：，搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 K： 盘展示/识别隐藏文件（未删除）；文件直接放 K： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 K： 盘展示/识别隐藏文件（未删除）；文件直接放 K： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 K： 盘展示/识别隐藏文件（未删除）；文件直接放 K： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 K： 盘中直接永久删除文件（不进回收站）；所有文件直接放 K： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 将样本文件直接放 K： 根目录；2) 选中文件按 Shift+Delete 并确认“永久删除”；3) 打开回收站确认看不到该文件；4) 扫描 K： 并搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 K： 盘中直接永久删除文件（不进回收站）；所有文件直接放 K： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 K： 盘中直接永久删除文件（不进回收站）；所有文件直接放 K： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 K： 盘中直接永久删除文件（不进回收站）；所有文件直接放 K： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并删除到回收站保留；文件直接放 K： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 样本放 K： 根目录并设为隐藏；2) 删除到回收站且不清空回收站；3) 扫描 K：；4) 搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并删除到回收站保留；文件直接放 K： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并删除到回收站保留；文件直接放 K： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并删除到回收站保留；文件直接放 K： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并删除后清空回收站；文件直接放 K： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 样本放 K： 根目录并设为隐藏；2) 删除到回收站后立即清空回收站；3) 扫描 K：；4) 搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并删除后清空回收站；文件直接放 K： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并删除后清空回收站；文件直接放 K： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并删除后清空回收站；文件直接放 K： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 K： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 样本放 K： 根目录并设为隐藏；2) Shift+Delete 永久删除；3) 回收站确认无该文件；4) 扫描 K： 并搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 K： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 K： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 K： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 K： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>1) 运行 stage_g_folder_samples.ps1 或建 K：\nest_L1\；2) 样本名 G_nest_L01_&lt;yyMMdd_HHmm&gt;.pptx；3) Delete→回收站保留；4) 扫 K： 看路径</t>
+  </si>
+  <si>
+    <t>能检出；路径含 K：\nest_L1\G_nest_L01_…</t>
+  </si>
+  <si>
+    <t>同上，路径 K：\nest_L1\nest_L2\nest_L3\</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J盘:U盘（ 232gb）功能用例 </t>
+  </si>
+  <si>
+    <t>用途： 范围：仅 : U盘（ 232gb）</t>
+  </si>
+  <si>
+    <t>在 j： 盘中删除文件并在回收站保留；所有文件直接放 j： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 j： 根目录，删除到回收站且不清空回收站，扫描 j：，在结果中搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 j： 盘中删除文件并在回收站保留；所有文件直接放 j： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 j： 根目录，删除到回收站且不清空回收站，扫描 j：，打开结果详情查看路径</t>
+  </si>
+  <si>
+    <t>展示删除前路径（应为 j：\文件名），路径可读且无乱码</t>
+  </si>
+  <si>
+    <t>在 j： 盘中删除文件并在回收站保留；所有文件直接放 j： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 j： 根目录，删除到回收站且不清空回收站，扫描 j：，在结果中点击预览</t>
+  </si>
+  <si>
+    <t>在 j： 盘中删除文件并在回收站保留；所有文件直接放 j： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 j： 根目录，删除到回收站且不清空回收站，扫描 j：，导出或恢复后本地打开核对内容</t>
+  </si>
+  <si>
+    <t>在 j： 盘中删除文件并清空回收站；所有文件直接放 j： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 j： 根目录，删除到回收站后立即清空回收站，扫描 j：，在结果中搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 j： 盘中删除文件并清空回收站；所有文件直接放 j： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 j： 根目录，删除到回收站后立即清空回收站，扫描 j：，打开结果详情查看路径</t>
+  </si>
+  <si>
+    <t>在 j： 盘中删除文件并清空回收站；所有文件直接放 j： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 j： 根目录，删除到回收站后立即清空回收站，扫描 j：，在结果中点击预览</t>
+  </si>
+  <si>
+    <t>在 j： 盘中删除文件并清空回收站；所有文件直接放 j： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>将样本文件直接放在 j： 根目录，删除到回收站后立即清空回收站，扫描 j：，导出或恢复后本地打开核对内容</t>
+  </si>
+  <si>
+    <t>在 j： 盘展示/识别隐藏文件（未删除）；文件直接放 j： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>样本放 j： 根目录并设为 Hidden（不删除），扫描 j：，搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 j： 盘展示/识别隐藏文件（未删除）；文件直接放 j： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 j： 盘展示/识别隐藏文件（未删除）；文件直接放 j： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 j： 盘展示/识别隐藏文件（未删除）；文件直接放 j： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 j： 盘中直接永久删除文件（不进回收站）；所有文件直接放 j： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 将样本文件直接放 j： 根目录；2) 选中文件按 Shift+Delete 并确认“永久删除”；3) 打开回收站确认看不到该文件；4) 扫描 j： 并搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 j： 盘中直接永久删除文件（不进回收站）；所有文件直接放 j： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 j： 盘中直接永久删除文件（不进回收站）；所有文件直接放 j： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 j： 盘中直接永久删除文件（不进回收站）；所有文件直接放 j： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并删除到回收站保留；文件直接放 j： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 样本放 j： 根目录并设为隐藏；2) 删除到回收站且不清空回收站；3) 扫描 j：；4) 搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并删除到回收站保留；文件直接放 j： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并删除到回收站保留；文件直接放 j： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并删除到回收站保留；文件直接放 j： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并删除后清空回收站；文件直接放 j： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 样本放 j： 根目录并设为隐藏；2) 删除到回收站后立即清空回收站；3) 扫描 j：；4) 搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并删除后清空回收站；文件直接放 j： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并删除后清空回收站；文件直接放 j： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并删除后清空回收站；文件直接放 j： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 j： 根目录（无文件夹）-检出</t>
+  </si>
+  <si>
+    <t>1) 样本放 j： 根目录并设为隐藏；2) Shift+Delete 永久删除；3) 回收站确认无该文件；4) 扫描 j： 并搜索目标文件名</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 j： 根目录（无文件夹）-原路径</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 j： 根目录（无文件夹）-预览</t>
+  </si>
+  <si>
+    <t>在 j： 盘创建隐藏文件并永久删除（不进回收站）；文件直接放 j： 根目录（无文件夹）-完整性</t>
+  </si>
+  <si>
+    <t>1) 运行 stage_g_folder_samples.ps1 或建 j：\nest_L1\；2) 样本名 G_nest_L01_&lt;yyMMdd_HHmm&gt;.pptx；3) Delete→回收站保留；4) 扫 j： 看路径</t>
+  </si>
+  <si>
+    <t>能检出；路径含 j：\nest_L1\G_nest_L01_…</t>
+  </si>
+  <si>
+    <t>同上，路径 j：\nest_L1\nest_L2\nest_L3\</t>
   </si>
 </sst>
 </file>
@@ -3265,4 +3697,2247 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="7" width="19.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" ht="67.5" spans="1:7">
+      <c r="A8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" ht="67.5" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" ht="67.5" spans="1:7">
+      <c r="A10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" ht="81" spans="1:7">
+      <c r="A11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" ht="67.5" spans="1:7">
+      <c r="A12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" ht="67.5" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" ht="67.5" spans="1:7">
+      <c r="A14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" ht="81" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" ht="54" spans="1:7">
+      <c r="A16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" ht="67.5" spans="1:7">
+      <c r="A17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" ht="54" spans="1:7">
+      <c r="A18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" ht="67.5" spans="1:7">
+      <c r="A19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" ht="108" spans="1:7">
+      <c r="A20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" ht="67.5" spans="1:7">
+      <c r="A21" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" ht="67.5" spans="1:7">
+      <c r="A22" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" ht="67.5" spans="1:7">
+      <c r="A23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" ht="67.5" spans="1:7">
+      <c r="A24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" ht="67.5" spans="1:7">
+      <c r="A25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" ht="67.5" spans="1:7">
+      <c r="A26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" ht="67.5" spans="1:7">
+      <c r="A27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" ht="81" spans="1:7">
+      <c r="A28" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" ht="67.5" spans="1:7">
+      <c r="A29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="30" ht="67.5" spans="1:7">
+      <c r="A30" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" ht="67.5" spans="1:7">
+      <c r="A31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" ht="81" spans="1:7">
+      <c r="A32" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" ht="67.5" spans="1:7">
+      <c r="A33" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" ht="67.5" spans="1:7">
+      <c r="A34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" ht="67.5" spans="1:7">
+      <c r="A35" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" ht="135" spans="1:7">
+      <c r="A36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" ht="40.5" spans="1:7">
+      <c r="A37" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" ht="27" spans="1:7">
+      <c r="A38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" ht="27" spans="1:7">
+      <c r="A39" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F1:F39">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"f"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="7" width="17.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" ht="27" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" ht="81" spans="1:7">
+      <c r="A8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" ht="81" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" ht="67.5" spans="1:7">
+      <c r="A10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" ht="81" spans="1:7">
+      <c r="A11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" ht="81" spans="1:7">
+      <c r="A12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" ht="81" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" ht="81" spans="1:7">
+      <c r="A14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" ht="81" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" ht="67.5" spans="1:7">
+      <c r="A16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" ht="67.5" spans="1:7">
+      <c r="A17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" ht="67.5" spans="1:7">
+      <c r="A18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" ht="67.5" spans="1:7">
+      <c r="A19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" ht="121.5" spans="1:7">
+      <c r="A20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" ht="81" spans="1:7">
+      <c r="A21" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" ht="67.5" spans="1:7">
+      <c r="A22" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" ht="81" spans="1:7">
+      <c r="A23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" ht="81" spans="1:7">
+      <c r="A24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" ht="67.5" spans="1:7">
+      <c r="A25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" ht="67.5" spans="1:7">
+      <c r="A26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" ht="67.5" spans="1:7">
+      <c r="A27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" ht="81" spans="1:7">
+      <c r="A28" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" ht="67.5" spans="1:7">
+      <c r="A29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="30" ht="67.5" spans="1:7">
+      <c r="A30" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" ht="67.5" spans="1:7">
+      <c r="A31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" ht="94.5" spans="1:7">
+      <c r="A32" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" ht="81" spans="1:7">
+      <c r="A33" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" ht="67.5" spans="1:7">
+      <c r="A34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" ht="81" spans="1:7">
+      <c r="A35" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" ht="135" spans="1:7">
+      <c r="A36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" ht="40.5" spans="1:7">
+      <c r="A37" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" ht="27" spans="1:7">
+      <c r="A38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" ht="27" spans="1:7">
+      <c r="A39" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F1:F39">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"f"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <cols>
+    <col min="1" max="7" width="23.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" ht="54" spans="1:7">
+      <c r="A8" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+    </row>
+    <row r="9" ht="54" spans="1:7">
+      <c r="A9" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" ht="54" spans="1:7">
+      <c r="A10" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="11" ht="67.5" spans="1:7">
+      <c r="A11" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" ht="54" spans="1:7">
+      <c r="A12" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" ht="54" spans="1:7">
+      <c r="A13" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" ht="54" spans="1:7">
+      <c r="A14" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="15" ht="67.5" spans="1:7">
+      <c r="A15" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" ht="54" spans="1:7">
+      <c r="A16" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" ht="54" spans="1:7">
+      <c r="A17" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" ht="54" spans="1:7">
+      <c r="A18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="19" ht="54" spans="1:7">
+      <c r="A19" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" ht="81" spans="1:7">
+      <c r="A20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="21" ht="54" spans="1:7">
+      <c r="A21" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F21" s="3"/>
+      <c r="G21" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="22" ht="54" spans="1:7">
+      <c r="A22" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="23" ht="54" spans="1:7">
+      <c r="A23" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" ht="54" spans="1:7">
+      <c r="A24" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="25" ht="54" spans="1:7">
+      <c r="A25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="26" ht="54" spans="1:7">
+      <c r="A26" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" ht="54" spans="1:7">
+      <c r="A27" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" ht="67.5" spans="1:7">
+      <c r="A28" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="29" ht="54" spans="1:7">
+      <c r="A29" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="30" ht="54" spans="1:7">
+      <c r="A30" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" ht="54" spans="1:7">
+      <c r="A31" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" ht="67.5" spans="1:7">
+      <c r="A32" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" ht="54" spans="1:7">
+      <c r="A33" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" ht="54" spans="1:7">
+      <c r="A34" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" ht="54" spans="1:7">
+      <c r="A35" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="36" ht="94.5" spans="1:7">
+      <c r="A36" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="37" ht="40.5" spans="1:7">
+      <c r="A37" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="38" ht="27" spans="1:7">
+      <c r="A38" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="39" ht="27" spans="1:7">
+      <c r="A39" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A5:G5"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F1:F39">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"f"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>